--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/wealth_data.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/wealth_data.xlsx
@@ -1,32 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gilbert.fontana\Desktop\R\16\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B236C8A4-9F77-423D-8AD6-5B6BDF00A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -35,58 +22,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="11">
   <si>
-    <t>year</t>
+    <t xml:space="preserve">year</t>
   </si>
   <si>
-    <t>country</t>
+    <t xml:space="preserve">country</t>
   </si>
   <si>
-    <t>total_wealth</t>
+    <t xml:space="preserve">total_wealth</t>
   </si>
   <si>
-    <t>China</t>
+    <t xml:space="preserve">China</t>
   </si>
   <si>
-    <t>France</t>
+    <t xml:space="preserve">France</t>
   </si>
   <si>
-    <t>Germany</t>
+    <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t>India</t>
+    <t xml:space="preserve">India</t>
   </si>
   <si>
-    <t>Japan</t>
+    <t xml:space="preserve">Japan</t>
   </si>
   <si>
-    <t>United Kingdom</t>
+    <t xml:space="preserve">United Kingdom</t>
   </si>
   <si>
-    <t>United States</t>
+    <t xml:space="preserve">United States</t>
   </si>
   <si>
-    <t>Other</t>
+    <t xml:space="preserve">Other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +103,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -106,40 +111,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -174,7 +200,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -209,7 +235,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,184 +270,142 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C177"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.63"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,1943 +416,1949 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>3704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>4704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>6160</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>1553</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>19404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>6565</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0" t="n">
         <v>43423</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0" t="n">
         <v>32331</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0" t="n">
         <v>4136</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0" t="n">
         <v>4645</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0" t="n">
         <v>5990</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0" t="n">
         <v>1733</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0" t="n">
         <v>16324</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0" t="n">
         <v>6555</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0" t="n">
         <v>45043</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0" t="n">
         <v>31736</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0" t="n">
         <v>4771</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0" t="n">
         <v>5921</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0" t="n">
         <v>7146</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="0" t="n">
         <v>2004</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="0" t="n">
         <v>17765</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="0" t="n">
         <v>7912</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="0" t="n">
         <v>45185</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
         <v>2002</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="0" t="n">
         <v>38045</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="0" t="n">
         <v>5668</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="0" t="n">
         <v>7979</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="0" t="n">
         <v>8955</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="0" t="n">
         <v>2432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="0" t="n">
         <v>19816</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="0" t="n">
         <v>9557</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="0" t="n">
         <v>50231</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
         <v>2003</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="0" t="n">
         <v>48382</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="0" t="n">
         <v>6840</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="0" t="n">
         <v>9833</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="0" t="n">
         <v>10027</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="0" t="n">
         <v>2935</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="0" t="n">
         <v>20131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="0" t="n">
         <v>11385</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="0" t="n">
         <v>57066</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
         <v>2004</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="0" t="n">
         <v>57202</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="0" t="n">
         <v>8522</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="0" t="n">
         <v>9679</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="0" t="n">
         <v>9073</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="0" t="n">
         <v>3266</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="0" t="n">
         <v>19476</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="0" t="n">
         <v>10949</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="0" t="n">
         <v>62634</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
         <v>2005</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="0" t="n">
         <v>58751</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="0" t="n">
         <v>10394</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="0" t="n">
         <v>12040</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="0" t="n">
         <v>10344</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="0" t="n">
         <v>3833</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="0" t="n">
         <v>19686</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="0" t="n">
         <v>13296</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="0" t="n">
         <v>66897</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
         <v>2006</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="0" t="n">
         <v>70942</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="0" t="n">
         <v>14010</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="0" t="n">
         <v>14281</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="0" t="n">
         <v>12302</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="0" t="n">
         <v>4985</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="0" t="n">
         <v>20152</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="0" t="n">
         <v>14524</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="0" t="n">
         <v>68235</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="0" t="n">
         <v>84883</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="0" t="n">
         <v>17723</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="0" t="n">
         <v>12907</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68">
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="0" t="n">
         <v>11630</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="0" t="n">
         <v>4663</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="0" t="n">
         <v>24129</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="0" t="n">
         <v>9513</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="0" t="n">
         <v>59478</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="0" t="n">
         <v>76574</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="0" t="n">
         <v>19986</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="0" t="n">
         <v>13369</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="0" t="n">
         <v>12425</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="0" t="n">
         <v>5645</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="0" t="n">
         <v>23743</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="0" t="n">
         <v>11193</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="0" t="n">
         <v>61171</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="0" t="n">
         <v>85453</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="0" t="n">
         <v>25493</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="0" t="n">
         <v>13526</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="0" t="n">
         <v>11934</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="0" t="n">
         <v>6810</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="0" t="n">
         <v>28640</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="0" t="n">
         <v>11199</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="0" t="n">
         <v>64661</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="0" t="n">
         <v>89622</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90">
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="0" t="n">
         <v>30920</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="0" t="n">
         <v>13428</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="0" t="n">
         <v>11900</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93">
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="0" t="n">
         <v>6607</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="0" t="n">
         <v>29718</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95">
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="0" t="n">
         <v>11619</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="0" t="n">
         <v>65788</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="0" t="n">
         <v>90981</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="0" t="n">
         <v>34611</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="0" t="n">
         <v>13384</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="0" t="n">
         <v>12665</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="0" t="n">
         <v>7353</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="0" t="n">
         <v>27161</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="0" t="n">
         <v>12190</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="0" t="n">
         <v>70808</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="0" t="n">
         <v>98580</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="0" t="n">
         <v>40826</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="0" t="n">
         <v>14098</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="0" t="n">
         <v>13846</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="0" t="n">
         <v>7541</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="0" t="n">
         <v>23122</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="0" t="n">
         <v>13269</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="0" t="n">
         <v>79226</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="0" t="n">
         <v>103366</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="0" t="n">
         <v>44887</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115">
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="0" t="n">
         <v>12461</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="0" t="n">
         <v>12799</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="0" t="n">
         <v>8283</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="0" t="n">
         <v>21004</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119">
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="0" t="n">
         <v>14017</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="0" t="n">
         <v>85106</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="0" t="n">
         <v>99197</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="0" t="n">
         <v>46535</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="0" t="n">
         <v>11594</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="0" t="n">
         <v>12009</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="0" t="n">
         <v>8948</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="0" t="n">
         <v>21519</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="0" t="n">
         <v>13978</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128">
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="0" t="n">
         <v>87959</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129">
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="0" t="n">
         <v>95156</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130">
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="0" t="n">
         <v>52028</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131">
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="0" t="n">
         <v>11729</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132">
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="0" t="n">
         <v>12160</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133">
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="0" t="n">
         <v>9886</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134">
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="0" t="n">
         <v>22364</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135">
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="0" t="n">
         <v>12593</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136">
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="0" t="n">
         <v>93094</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137">
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="0" t="n">
         <v>97837</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138">
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="0" t="n">
         <v>62361</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139">
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="0" t="n">
         <v>13845</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="0" t="n">
         <v>14637</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141">
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="0" t="n">
         <v>11769</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142">
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="0" t="n">
         <v>23854</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143">
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="0" t="n">
         <v>14501</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144">
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="0" t="n">
         <v>101817</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145">
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="0" t="n">
         <v>114962</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146">
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="0" t="n">
         <v>65943</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147">
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="0" t="n">
         <v>13470</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148">
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="0" t="n">
         <v>14681</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149">
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="0" t="n">
         <v>12182</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150">
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="0" t="n">
         <v>24075</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151">
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="0" t="n">
         <v>13331</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152">
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="0" t="n">
         <v>102376</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153">
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="0" t="n">
         <v>113005</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="0" t="n">
         <v>70211</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155">
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="0" t="n">
         <v>14063</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156">
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="0" t="n">
         <v>15356</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157">
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="0" t="n">
         <v>13264</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158">
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="0" t="n">
         <v>25303</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159">
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="0" t="n">
         <v>14082</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160">
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="0" t="n">
         <v>114896</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161">
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="0" t="n">
         <v>121405</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162">
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="0" t="n">
         <v>73940</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163">
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="0" t="n">
         <v>16282</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164">
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="0" t="n">
         <v>17390</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165">
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="0" t="n">
         <v>12700</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166">
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="0" t="n">
         <v>27261</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167">
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="0" t="n">
         <v>15676</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168">
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="0" t="n">
         <v>126300</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169">
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="0" t="n">
         <v>132568</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170">
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="0" t="n">
         <v>85107</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171">
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="0" t="n">
         <v>16159</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172">
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="0" t="n">
         <v>17489</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173">
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="0" t="n">
         <v>14225</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="0" t="n">
         <v>25692</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="0" t="n">
         <v>16261</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="0" t="n">
         <v>145793</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="0" t="n">
         <v>142841</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>